--- a/WorkBot/main/data/orders/Hillcrest Dairy/Hillcrest Dairy_Bakery_20260530.xlsx
+++ b/WorkBot/main/data/orders/Hillcrest Dairy/Hillcrest Dairy_Bakery_20260530.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -542,6 +542,69 @@
         <v>16.65</v>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>twog</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Milk - 2%</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>6</v>
+      </c>
+      <c r="D9" t="n">
+        <v>16.08</v>
+      </c>
+      <c r="E9" t="n">
+        <v>96.48</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>wholeg</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Milk - Whole</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>10</v>
+      </c>
+      <c r="D10" t="n">
+        <v>16.08</v>
+      </c>
+      <c r="E10" t="n">
+        <v>160.8</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>skimg</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Milk - Skim</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>4</v>
+      </c>
+      <c r="D11" t="n">
+        <v>15.56</v>
+      </c>
+      <c r="E11" t="n">
+        <v>62.24</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
